--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,12 +515,6 @@
     <t>va-tn</t>
   </si>
   <si>
-    <t>1994: source value from AR TRANSACTION - TRANSACTION NUMBER (433-.01)</t>
-  </si>
-  <si>
-    <t>IB.ARTransaction.TransactionNumber</t>
-  </si>
-  <si>
     <t>ChargeItem.identifier:va-tn.id</t>
   </si>
   <si>
@@ -759,6 +753,12 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1994: source value from AR TRANSACTION - TRANSACTION NUMBER (433-.01)</t>
+  </si>
+  <si>
+    <t>IB.ARTransaction.TransactionNumber</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
@@ -824,46 +824,46 @@
     <t>va-bn</t>
   </si>
   <si>
+    <t>ChargeItem.identifier:va-bn.id</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.extension</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.use</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.type</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.type.id</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.type.extension</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.type.coding</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.type.text</t>
+  </si>
+  <si>
+    <t>Bill Number</t>
+  </si>
+  <si>
+    <t>1995-1: fixed value = Bill Number</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.system</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier:va-bn.value</t>
+  </si>
+  <si>
     <t>1995: source value from AR TRANSACTION - TRANSACTION NUMBER (433-.03)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AccountsReceivableIEN,IB.ARTransaction.PatientIEN,IB.ARTransactionComment.PatientIEN,IB.ARTransactionDescription.PatientIEN,IB.ARTransactionFiscalYear.PatientIEN</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.id</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.extension</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.use</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.type</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.type.id</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.type.extension</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.type.coding</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.type.text</t>
-  </si>
-  <si>
-    <t>Bill Number</t>
-  </si>
-  <si>
-    <t>1995-1: fixed value = Bill Number</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.system</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier:va-bn.value</t>
   </si>
   <si>
     <t>ChargeItem.identifier:va-bn.period</t>
@@ -3213,7 +3213,7 @@
         <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>79</v>
@@ -3296,10 +3296,10 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>154</v>
@@ -3316,10 +3316,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3342,13 +3342,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3399,7 +3399,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3426,7 +3426,7 @@
         <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>79</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3466,7 +3466,7 @@
         <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>139</v>
@@ -3507,10 +3507,10 @@
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>79</v>
@@ -3519,7 +3519,7 @@
         <v>153</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3546,7 +3546,7 @@
         <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>79</v>
@@ -3554,10 +3554,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3583,16 +3583,16 @@
         <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3617,31 +3617,31 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3668,7 +3668,7 @@
         <v>133</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>79</v>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3702,19 +3702,19 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
@@ -3739,31 +3739,31 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3787,10 +3787,10 @@
         <v>79</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>79</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3824,13 +3824,13 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3881,7 +3881,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3908,7 +3908,7 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3916,10 +3916,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3948,7 +3948,7 @@
         <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>139</v>
@@ -3989,10 +3989,10 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
@@ -4001,7 +4001,7 @@
         <v>153</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4028,7 +4028,7 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4062,19 +4062,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4123,7 +4123,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4147,10 +4147,10 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4184,19 +4184,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4206,7 +4206,7 @@
         <v>79</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>79</v>
@@ -4245,7 +4245,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4260,19 +4260,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4309,16 +4309,16 @@
         <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4331,7 +4331,7 @@
         <v>79</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>79</v>
@@ -4367,7 +4367,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4391,10 +4391,10 @@
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4419,7 +4419,7 @@
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>79</v>
@@ -4428,16 +4428,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4451,7 +4451,7 @@
         <v>79</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>79</v>
@@ -4487,7 +4487,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4502,10 +4502,10 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4779,7 +4779,7 @@
         <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>79</v>
@@ -4862,10 +4862,10 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>154</v>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4908,13 +4908,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4965,7 +4965,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4992,7 +4992,7 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -5000,10 +5000,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5032,7 +5032,7 @@
         <v>137</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>139</v>
@@ -5073,10 +5073,10 @@
         <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
@@ -5085,7 +5085,7 @@
         <v>153</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5112,7 +5112,7 @@
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -5120,10 +5120,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5149,16 +5149,16 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5183,31 +5183,31 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5234,7 +5234,7 @@
         <v>133</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5242,10 +5242,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5268,19 +5268,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5305,31 +5305,31 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5353,10 +5353,10 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
@@ -5364,10 +5364,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5390,13 +5390,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5447,7 +5447,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5474,7 +5474,7 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5482,10 +5482,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5514,7 +5514,7 @@
         <v>137</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>139</v>
@@ -5555,10 +5555,10 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>79</v>
@@ -5567,7 +5567,7 @@
         <v>153</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5594,7 +5594,7 @@
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5602,10 +5602,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5628,19 +5628,19 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5689,7 +5689,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5713,10 +5713,10 @@
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5750,19 +5750,19 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5772,7 +5772,7 @@
         <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>79</v>
@@ -5811,7 +5811,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5826,7 +5826,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -5835,10 +5835,10 @@
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5846,10 +5846,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5875,16 +5875,16 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5897,7 +5897,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5933,7 +5933,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5957,10 +5957,10 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
@@ -5968,10 +5968,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5985,7 +5985,7 @@
         <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -5994,16 +5994,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6017,7 +6017,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -6053,7 +6053,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6068,10 +6068,10 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -6623,7 +6623,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>292</v>
@@ -6828,7 +6828,7 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>308</v>
@@ -6946,13 +6946,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7003,7 +7003,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7030,7 +7030,7 @@
         <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7070,7 +7070,7 @@
         <v>137</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>139</v>
@@ -7111,10 +7111,10 @@
         <v>79</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>79</v>
@@ -7123,7 +7123,7 @@
         <v>153</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7150,7 +7150,7 @@
         <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7184,19 +7184,19 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7245,7 +7245,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7269,10 +7269,10 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7306,19 +7306,19 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7367,7 +7367,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7391,10 +7391,10 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -8026,13 +8026,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8083,7 +8083,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8110,7 +8110,7 @@
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8150,7 +8150,7 @@
         <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -8203,7 +8203,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8230,7 +8230,7 @@
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>79</v>
@@ -8386,7 +8386,7 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>373</v>
@@ -9102,7 +9102,7 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>407</v>
@@ -9462,7 +9462,7 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>426</v>
@@ -9822,7 +9822,7 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>441</v>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -860,7 +860,7 @@
     <t>ChargeItem.identifier:va-bn.value</t>
   </si>
   <si>
-    <t>1995: source value from AR TRANSACTION - TRANSACTION NUMBER (433-.03)</t>
+    <t>1995: source value from AR TRANSACTION - BILL NUMBER (433-.03)</t>
   </si>
   <si>
     <t>IB.ARTransaction.AccountsReceivableIEN,IB.ARTransaction.PatientIEN,IB.ARTransactionComment.PatientIEN,IB.ARTransactionDescription.PatientIEN,IB.ARTransactionFiscalYear.PatientIEN</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file AR TRANSACTION (433) to ChargeItem</t>
+    <t>This StructureDefinition contains the maps for VistA file AR TRANSACTION (433) to ChargeItem.</t>
   </si>
   <si>
     <t>Purpose</t>
